--- a/utils/monday_sprint_sprint_2023-21.xlsx
+++ b/utils/monday_sprint_sprint_2023-21.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="170">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>22473</t>
+    <t>5312735197</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>11/10/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>19/10/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>22110</t>
+    <t>5231831799</t>
   </si>
   <si>
     <t>Ação - Sistema de Movimentação de Amostra - Setor 596</t>
@@ -111,13 +111,16 @@
     <t>27/09/2023</t>
   </si>
   <si>
+    <t>21/10/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
     <t>Setembro</t>
   </si>
   <si>
-    <t>22388</t>
+    <t>5209299837</t>
   </si>
   <si>
     <t>Criar relatório do Qlik sense - Entradas no depósito x tempos orçado de acabamento (FTF) x Horas apontadas</t>
@@ -126,7 +129,7 @@
     <t>22/09/2023</t>
   </si>
   <si>
-    <t>22027</t>
+    <t>5122976366</t>
   </si>
   <si>
     <t>Tabelas para Aplicação QlikSense</t>
@@ -135,10 +138,13 @@
     <t>07/09/2023</t>
   </si>
   <si>
+    <t>18/10/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
-    <t>22598</t>
+    <t>5290593594</t>
   </si>
   <si>
     <t>Listagem de tabelas de informações de corridas</t>
@@ -147,25 +153,34 @@
     <t>06/10/2023</t>
   </si>
   <si>
-    <t>22594</t>
+    <t>10/10/2023</t>
+  </si>
+  <si>
+    <t>5290781623</t>
   </si>
   <si>
     <t>Controlar período de geração de arquivos carteira</t>
   </si>
   <si>
-    <t>22583</t>
+    <t>5290800996</t>
   </si>
   <si>
     <t>Sistema altona x benner - relatório OCs x vectos</t>
   </si>
   <si>
-    <t>22572</t>
+    <t>12/10/2023</t>
+  </si>
+  <si>
+    <t>5290891377</t>
   </si>
   <si>
     <t>Alteração do tipo de manutenção na abertura de SS</t>
   </si>
   <si>
-    <t>22570</t>
+    <t>09/10/2023</t>
+  </si>
+  <si>
+    <t>5290924831</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -174,55 +189,64 @@
     <t>PDI Eletrônico</t>
   </si>
   <si>
-    <t>22567</t>
+    <t>15/10/2023</t>
+  </si>
+  <si>
+    <t>5290956185</t>
   </si>
   <si>
     <t>Integração sistema Manutenção x Contabilidade</t>
   </si>
   <si>
-    <t>22556</t>
+    <t>5290994507</t>
   </si>
   <si>
     <t>E-mails automáticos - Sistema de desmoldagem</t>
   </si>
   <si>
-    <t>22550</t>
+    <t>5291015162</t>
   </si>
   <si>
     <t>Pergunta na aplicação Checklist Usinagem</t>
   </si>
   <si>
-    <t>22538</t>
+    <t>5291031574</t>
   </si>
   <si>
     <t>Habilitar a impressão em EDITAR ROMANEIO</t>
   </si>
   <si>
-    <t>22522</t>
+    <t>16/10/2023</t>
+  </si>
+  <si>
+    <t>5291066382</t>
   </si>
   <si>
     <t>Acrescentar cliente no relatório de apontamento</t>
   </si>
   <si>
-    <t>22474</t>
+    <t>5291092515</t>
   </si>
   <si>
     <t>Alerta na SIC de investimentos</t>
   </si>
   <si>
-    <t>22517</t>
+    <t>5291111442</t>
   </si>
   <si>
     <t>Registro de luminosidade</t>
   </si>
   <si>
-    <t>22319</t>
+    <t>17/10/2023</t>
+  </si>
+  <si>
+    <t>5209574090</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Itens Comerciais</t>
   </si>
   <si>
-    <t>21214</t>
+    <t>5141375989</t>
   </si>
   <si>
     <t>Opção para consultar imagens</t>
@@ -231,31 +255,43 @@
     <t>11/09/2023</t>
   </si>
   <si>
-    <t>22455</t>
+    <t>5309133687</t>
   </si>
   <si>
     <t>Quando filtramos um cargo</t>
   </si>
   <si>
-    <t>10/10/2023</t>
+    <t>5309136042</t>
   </si>
   <si>
     <t>Problema para alterar/substituir arquivo</t>
   </si>
   <si>
+    <t>5309137272</t>
+  </si>
+  <si>
     <t>Quando um usuário faz login não entra direto</t>
   </si>
   <si>
+    <t>5309138330</t>
+  </si>
+  <si>
     <t>Não está em ordem alfabética os filtros</t>
   </si>
   <si>
+    <t>5309139761</t>
+  </si>
+  <si>
     <t>Dentro da relação de procedimentos</t>
   </si>
   <si>
+    <t>5309141277</t>
+  </si>
+  <si>
     <t>Quando não for conta administrador</t>
   </si>
   <si>
-    <t>22683</t>
+    <t>5312493609</t>
   </si>
   <si>
     <t>SIC - Ajustes</t>
@@ -264,31 +300,31 @@
     <t>Não definida</t>
   </si>
   <si>
-    <t>22674</t>
+    <t>5314745065</t>
   </si>
   <si>
     <t>Calculo MPS a partir da data Moldagem</t>
   </si>
   <si>
-    <t>22639</t>
+    <t>5290491283</t>
   </si>
   <si>
     <t>Saldo do Deposito / Controle de Embalagem Part.01</t>
   </si>
   <si>
-    <t>22530</t>
+    <t>5291046929</t>
   </si>
   <si>
     <t>Distribuição de sequencias por quantidade de estoque</t>
   </si>
   <si>
-    <t>22318</t>
+    <t>5209584659</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Modelos Revenda</t>
   </si>
   <si>
-    <t>21500</t>
+    <t>5054182558</t>
   </si>
   <si>
     <t>Grupo de etapas no CPP</t>
@@ -300,43 +336,67 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>22557</t>
+    <t>5308998224</t>
   </si>
   <si>
     <t>Quando coluna cota for "cota"</t>
   </si>
   <si>
+    <t>5309022427</t>
+  </si>
+  <si>
     <t>Na tela de inspeção, solicitar primeiro o cabeçalho e em uma segunda tela</t>
   </si>
   <si>
+    <t>5309029736</t>
+  </si>
+  <si>
     <t>Para cada cota solicitar 2 valores e consistir os dois com a cota</t>
   </si>
   <si>
+    <t>5309047221</t>
+  </si>
+  <si>
     <t>Na criação do CheckList importar as imagens do Croqui</t>
   </si>
   <si>
+    <t>5309051858</t>
+  </si>
+  <si>
     <t>Consistir modelo / desenho e revisão</t>
   </si>
   <si>
-    <t>22466</t>
+    <t>5312382962</t>
   </si>
   <si>
     <t>Alterar o label para “Adicionar”</t>
   </si>
   <si>
+    <t>5312384680</t>
+  </si>
+  <si>
     <t>Colocar o campo de quantidade no segundo nivel</t>
   </si>
   <si>
+    <t>5312386580</t>
+  </si>
+  <si>
     <t>Icluir nome do apontador no rodapé da página</t>
   </si>
   <si>
+    <t>5312389059</t>
+  </si>
+  <si>
     <t>Verificar titulos das telas</t>
   </si>
   <si>
+    <t>5312390497</t>
+  </si>
+  <si>
     <t>Criar tela de consulta de apontamentos não finalizados</t>
   </si>
   <si>
-    <t>22014</t>
+    <t>5312677545</t>
   </si>
   <si>
     <t>Receber processo</t>
@@ -345,6 +405,9 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>5309143079</t>
+  </si>
+  <si>
     <t>Criar log de acessos por colaborador</t>
   </si>
   <si>
@@ -357,6 +420,9 @@
     <t>Atividades Diversas</t>
   </si>
   <si>
+    <t>22/10/2023</t>
+  </si>
+  <si>
     <t>5307790596</t>
   </si>
   <si>
@@ -369,7 +435,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-21</t>
+    <t>Ago/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -427,6 +493,9 @@
   </si>
   <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1014,7 +1083,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1023,15 +1092,15 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1043,10 +1112,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1058,10 +1127,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1070,15 +1139,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1090,10 +1159,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1105,10 +1174,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1117,15 +1186,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1137,34 +1206,34 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1172,7 +1241,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1184,25 +1253,25 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1211,7 +1280,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1219,7 +1288,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1231,10 +1300,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1246,10 +1315,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1258,7 +1327,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1266,7 +1335,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1278,10 +1347,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1293,10 +1362,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1305,7 +1374,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1313,22 +1382,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1340,10 +1409,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1352,7 +1421,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1360,7 +1429,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1372,26 +1441,26 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
       </c>
@@ -1399,7 +1468,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1407,7 +1476,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1419,10 +1488,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1434,10 +1503,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1446,7 +1515,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1454,7 +1523,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1466,10 +1535,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1481,10 +1550,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1493,7 +1562,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -1501,7 +1570,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1513,10 +1582,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1528,10 +1597,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1540,7 +1609,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1548,7 +1617,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1560,10 +1629,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1575,10 +1644,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1587,7 +1656,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1595,7 +1664,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1607,10 +1676,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1622,10 +1691,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1634,7 +1703,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1642,7 +1711,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1654,10 +1723,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1669,10 +1738,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1681,7 +1750,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1689,7 +1758,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1701,10 +1770,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1716,10 +1785,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1728,30 +1797,30 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1763,10 +1832,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1778,27 +1847,27 @@
         <v>27</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1810,10 +1879,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1830,22 +1899,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1857,10 +1926,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1877,22 +1946,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1904,10 +1973,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1924,22 +1993,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1951,10 +2020,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1971,22 +2040,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1998,10 +2067,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2018,22 +2087,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2045,10 +2114,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2065,7 +2134,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2077,13 +2146,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2095,7 +2164,7 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2112,22 +2181,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2142,7 +2211,7 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2159,7 +2228,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2171,10 +2240,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2186,7 +2255,7 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
@@ -2198,7 +2267,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2206,7 +2275,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2218,10 +2287,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2233,10 +2302,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2245,7 +2314,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2253,7 +2322,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2265,10 +2334,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2280,10 +2349,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2292,15 +2361,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2312,10 +2381,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2327,10 +2396,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2339,30 +2408,30 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2374,10 +2443,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2394,22 +2463,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2421,10 +2490,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2441,22 +2510,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2468,10 +2537,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2488,22 +2557,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2515,10 +2584,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2535,22 +2604,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2562,10 +2631,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2582,7 +2651,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2594,10 +2663,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2612,7 +2681,7 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2629,7 +2698,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2641,10 +2710,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2659,7 +2728,7 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2676,7 +2745,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2688,10 +2757,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2706,7 +2775,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2723,7 +2792,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2735,10 +2804,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2753,7 +2822,7 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2770,7 +2839,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2782,10 +2851,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2800,7 +2869,7 @@
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2817,25 +2886,25 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>21</v>
@@ -2847,7 +2916,7 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2864,22 +2933,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2891,10 +2960,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2911,25 +2980,25 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -2938,10 +3007,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -2958,25 +3027,25 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
@@ -2985,10 +3054,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3005,25 +3074,25 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>21</v>
@@ -3032,10 +3101,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3063,23 +3132,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3087,16 +3156,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3107,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>10.87</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3115,7 +3184,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3128,7 +3197,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3136,7 +3205,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3167,12 +3236,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>45</v>
@@ -3186,7 +3255,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3196,25 +3265,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3231,13 +3300,13 @@
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3249,21 +3318,21 @@
         <v>45</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -3275,13 +3344,13 @@
         <v>45</v>
       </c>
       <c r="M11" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="Q11">
         <v>25</v>
@@ -3289,7 +3358,7 @@
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3301,33 +3370,33 @@
         <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3335,13 +3404,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H14">
         <v>4</v>
       </c>
       <c r="M14" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3349,7 +3418,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3357,7 +3426,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3365,7 +3434,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3373,10 +3442,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3384,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3392,142 +3461,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="2">
         <v>44</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
